--- a/sequences/learning_blockA_fixed-middle-10_01.xlsx
+++ b/sequences/learning_blockA_fixed-middle-10_01.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -614,18 +614,18 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -678,7 +678,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -698,33 +698,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -740,7 +740,7 @@
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -767,17 +767,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -807,19 +807,19 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -861,7 +861,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -965,17 +965,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,43 +985,43 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1031,13 +1031,13 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_02.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_39.jpg</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7</v>
-      </c>
       <c r="W7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1158,84 +1158,84 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1257,52 +1257,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_01.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1318,23 +1318,23 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
         <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S10" t="n">
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
         <v>5</v>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1516,23 +1516,23 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
         <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1599,16 +1599,16 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0.3</v>
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1683,54 +1683,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0.1</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
         <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,38 +1881,38 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1925,10 +1925,10 @@
         <v>11</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2004,14 +2004,14 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,10 +2024,10 @@
         <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2074,43 +2074,43 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2120,13 +2120,13 @@
         <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2178,17 +2178,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,34 +2198,34 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2318,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
         <v>14</v>
@@ -2346,17 +2346,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2391,19 +2391,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -2414,13 +2414,13 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
         <v>8</v>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2485,41 +2485,41 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" t="n">
         <v>0.5</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S21" t="n">
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
         <v>16</v>
@@ -2544,17 +2544,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2605,20 +2605,20 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
         <v>17</v>
@@ -2643,42 +2643,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2688,19 +2688,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2810,13 +2810,13 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
         <v>9</v>
@@ -2841,84 +2841,84 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_10.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_03.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S25" t="n">
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="n">
-        <v>10</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5</v>
-      </c>
       <c r="W25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,14 +2970,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>center</t>
@@ -2985,19 +2985,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" t="n">
         <v>0.6</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.1</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U26" t="n">
         <v>17</v>
       </c>
       <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="n">
         <v>2</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3049,14 +3049,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>phone</t>
@@ -3069,22 +3069,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3093,14 +3093,14 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,10 +3113,10 @@
         <v>16</v>
       </c>
       <c r="V27" t="n">
+        <v>4</v>
+      </c>
+      <c r="W27" t="n">
         <v>6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3195,7 +3195,7 @@
         <v>0.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3212,10 +3212,10 @@
         <v>11</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3282,19 +3282,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
         <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3465,54 +3465,54 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S31" t="n">
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -3539,17 +3539,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3584,18 +3584,18 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -3605,13 +3605,13 @@
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -3633,42 +3633,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3678,19 +3678,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3732,47 +3732,47 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3782,34 +3782,34 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="W34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3885,27 +3885,27 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q35" t="n">
         <v>0.3</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W35" t="n">
         <v>5</v>
@@ -3930,84 +3930,84 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S36" t="n">
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
@@ -4029,52 +4029,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4083,30 +4083,30 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4128,84 +4128,84 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_10.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_03.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_08.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_40.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>8</v>
+      </c>
+      <c r="V38" t="n">
+        <v>16</v>
+      </c>
+      <c r="W38" t="n">
         <v>4</v>
-      </c>
-      <c r="U38" t="n">
-        <v>10</v>
-      </c>
-      <c r="V38" t="n">
-        <v>17</v>
-      </c>
-      <c r="W38" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4237,17 +4237,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U39" t="n">
         <v>17</v>
       </c>
       <c r="V39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4366,28 +4366,28 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,7 +4400,7 @@
         <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W40" t="n">
         <v>6</v>
@@ -4435,14 +4435,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_02.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>lamp</t>
@@ -4455,38 +4455,38 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>11</v>
       </c>
       <c r="V41" t="n">
+        <v>10</v>
+      </c>
+      <c r="W41" t="n">
         <v>3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4554,38 +4554,38 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P42" t="n">
         <v>0.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4598,10 +4598,10 @@
         <v>5</v>
       </c>
       <c r="V42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4694,7 +4694,7 @@
         <v>5</v>
       </c>
       <c r="U43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
         <v>2</v>
@@ -4722,42 +4722,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4790,16 +4790,16 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4846,17 +4846,17 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P45" t="n">
         <v>0.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4892,13 +4892,13 @@
         <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W45" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -4920,52 +4920,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4977,27 +4977,27 @@
         <v>0.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S46" t="n">
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5034,17 +5034,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -5080,23 +5080,23 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>14</v>
       </c>
       <c r="W47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -5118,44 +5118,44 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>stimuli/phone/phone_40.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>car</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>center</t>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.4</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V48" t="n">
+        <v>17</v>
+      </c>
+      <c r="W48" t="n">
         <v>11</v>
-      </c>
-      <c r="W48" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -5217,52 +5217,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5271,30 +5271,30 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S49" t="n">
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V49" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -5316,52 +5316,52 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5370,30 +5370,30 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S50" t="n">
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="W50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -5415,84 +5415,84 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S51" t="n">
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V51" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5549,22 +5549,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -5575,14 +5575,14 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S52" t="n">
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U52" t="n">
         <v>17</v>
@@ -5591,7 +5591,7 @@
         <v>16</v>
       </c>
       <c r="W52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,38 +5643,38 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0.2</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5687,10 +5687,10 @@
         <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5747,33 +5747,33 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P54" t="n">
         <v>0.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5789,7 +5789,7 @@
         <v>2</v>
       </c>
       <c r="W54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5861,18 +5861,18 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5885,10 +5885,10 @@
         <v>5</v>
       </c>
       <c r="V55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -5915,17 +5915,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5935,43 +5935,43 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5981,13 +5981,13 @@
         <v>5</v>
       </c>
       <c r="U56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -6009,47 +6009,47 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -6070,23 +6070,23 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S57" t="n">
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U57" t="n">
         <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -6113,17 +6113,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6133,17 +6133,17 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -6179,13 +6179,13 @@
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -6207,42 +6207,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6264,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -6275,16 +6275,16 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V59" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -6306,42 +6306,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6374,16 +6374,16 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U60" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -6405,84 +6405,84 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S61" t="n">
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V61" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q62" t="n">
         <v>0.3</v>
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_01.jpg</t>
+          <t>stimuli/pencil/pencil_08.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -6702,17 +6702,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6722,17 +6722,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6752,31 +6752,31 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q64" t="n">
         <v>0.4</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V64" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W64" t="n">
         <v>2</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/car/car_13.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,17 +6831,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6851,34 +6851,34 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S65" t="n">
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U65" t="n">
         <v>17</v>
       </c>
       <c r="V65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>5</v>
       </c>
       <c r="W66" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7073,10 +7073,10 @@
         <v>11</v>
       </c>
       <c r="V67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_08.jpg</t>
+          <t>stimuli/phone/phone_40.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,38 +7128,38 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P68" t="n">
         <v>0.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>5</v>
       </c>
       <c r="V68" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
@@ -7202,19 +7202,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>dog</t>
@@ -7222,27 +7222,27 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -7268,13 +7268,13 @@
         <v>5</v>
       </c>
       <c r="U69" t="n">
+        <v>4</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>8</v>
-      </c>
-      <c r="V69" t="n">
-        <v>9</v>
-      </c>
-      <c r="W69" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7336,17 +7336,17 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -7357,20 +7357,20 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S70" t="n">
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U70" t="n">
         <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W70" t="n">
         <v>16</v>
@@ -7400,12 +7400,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7466,10 +7466,10 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W71" t="n">
         <v>17</v>
@@ -7494,12 +7494,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7529,17 +7529,17 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7555,23 +7555,23 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S72" t="n">
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V72" t="n">
         <v>11</v>
       </c>
       <c r="W72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -7661,13 +7661,13 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U73" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W73" t="n">
         <v>16</v>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7707,17 +7707,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7727,49 +7727,49 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P74" t="n">
         <v>0.6</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S74" t="n">
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V74" t="n">
         <v>14</v>
       </c>
       <c r="W74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7806,17 +7806,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7826,49 +7826,49 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P75" t="n">
         <v>0.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S75" t="n">
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V75" t="n">
         <v>5</v>
       </c>
       <c r="W75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -7890,42 +7890,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_40.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7935,19 +7935,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V76" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -7989,42 +7989,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/car/car_13.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -8057,16 +8057,16 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V77" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8098,17 +8098,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/lamp/lamp_01.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,54 +8118,54 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S78" t="n">
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U78" t="n">
         <v>17</v>
       </c>
       <c r="V78" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8232,19 +8232,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P79" t="n">
         <v>0.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>16</v>
       </c>
       <c r="V79" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W79" t="n">
         <v>6</v>
